--- a/Data/27/Workday_NewHire_Portugal_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_Portugal_Regression_PK17.xlsx
@@ -214,7 +214,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699397</t>
+    <t>10699529</t>
   </si>
   <si>
     <t>Passed</t>
@@ -226,10 +226,10 @@
     <t>Portugal</t>
   </si>
   <si>
-    <t>Joanie</t>
-  </si>
-  <si>
-    <t>Reichert</t>
+    <t>Evelyn</t>
+  </si>
+  <si>
+    <t>Grimes</t>
   </si>
   <si>
     <t>Sr.</t>
@@ -340,7 +340,7 @@
     <t>ID Number (Numero de</t>
   </si>
   <si>
-    <t>24982928 2AP53</t>
+    <t>24982928 2AP55</t>
   </si>
   <si>
     <t>BBVAESMM128</t>
@@ -355,16 +355,16 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699398</t>
+    <t>10699530</t>
   </si>
   <si>
     <t>420 Store Management (Rilyv Zisozy (4206015))</t>
   </si>
   <si>
-    <t>Jamison</t>
-  </si>
-  <si>
-    <t>Von</t>
+    <t>Nathanael</t>
+  </si>
+  <si>
+    <t>Waters-Mann</t>
   </si>
   <si>
     <t>Sra.</t>
@@ -373,7 +373,7 @@
     <t>New</t>
   </si>
   <si>
-    <t>Auto 82426804</t>
+    <t>Auto 79934795</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -391,7 +391,7 @@
     <t>Single</t>
   </si>
   <si>
-    <t>24982928 2AP54</t>
+    <t>24982928 2AP56</t>
   </si>
 </sst>
 </file>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="L2" s="20">
         <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45773</v>
+        <v>45779</v>
       </c>
       <c r="M2" s="15" t="s">
         <v>68</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="U2" s="20">
         <f t="shared" ref="U2:U3" si="1">L2</f>
-        <v>45773</v>
+        <v>45779</v>
       </c>
       <c r="V2" s="19" t="s">
         <v>79</v>
@@ -1357,11 +1357,11 @@
       </c>
       <c r="AL2" s="22">
         <f t="shared" ref="AL2:AL3" si="2">TODAY()+60</f>
-        <v>45864</v>
+        <v>45870</v>
       </c>
       <c r="AM2" s="22">
         <f t="shared" ref="AM2:AM3" si="3">U2</f>
-        <v>45773</v>
+        <v>45779</v>
       </c>
       <c r="AN2" s="30" t="s">
         <v>93</v>
@@ -1419,7 +1419,7 @@
         <v>104</v>
       </c>
       <c r="BF2" s="34">
-        <v>10000895705</v>
+        <v>10000895708</v>
       </c>
       <c r="BG2" s="33" t="s">
         <v>68</v>
@@ -1428,7 +1428,7 @@
         <v>105</v>
       </c>
       <c r="BI2" s="34">
-        <v>100845904</v>
+        <v>100845907</v>
       </c>
       <c r="BJ2" s="33" t="s">
         <v>68</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="L3" s="20">
         <f t="shared" si="0"/>
-        <v>45773</v>
+        <v>45779</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>68</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="U3" s="20">
         <f t="shared" si="1"/>
-        <v>45773</v>
+        <v>45779</v>
       </c>
       <c r="V3" s="19" t="s">
         <v>117</v>
@@ -1575,11 +1575,11 @@
       </c>
       <c r="AL3" s="22">
         <f t="shared" si="2"/>
-        <v>45864</v>
+        <v>45870</v>
       </c>
       <c r="AM3" s="22">
         <f t="shared" si="3"/>
-        <v>45773</v>
+        <v>45779</v>
       </c>
       <c r="AN3" s="30" t="s">
         <v>121</v>
@@ -1637,7 +1637,7 @@
         <v>104</v>
       </c>
       <c r="BF3" s="34">
-        <v>10000895706</v>
+        <v>10000895709</v>
       </c>
       <c r="BG3" s="33" t="s">
         <v>68</v>
@@ -1646,7 +1646,7 @@
         <v>105</v>
       </c>
       <c r="BI3" s="34">
-        <v>100845905</v>
+        <v>100845908</v>
       </c>
       <c r="BJ3" s="33" t="s">
         <v>68</v>

--- a/Data/27/Workday_NewHire_Portugal_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_Portugal_Regression_PK17.xlsx
@@ -1,23 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{1C6E3993-62BE-490C-B14A-B5F32166C46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BY$53</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="122">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -214,12 +229,6 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699529</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>420 Recruitment (Gozyb Sosobo (10034456))</t>
   </si>
   <si>
@@ -340,9 +349,6 @@
     <t>ID Number (Numero de</t>
   </si>
   <si>
-    <t>24982928 2AP55</t>
-  </si>
-  <si>
     <t>BBVAESMM128</t>
   </si>
   <si>
@@ -355,9 +361,6 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699530</t>
-  </si>
-  <si>
     <t>420 Store Management (Rilyv Zisozy (4206015))</t>
   </si>
   <si>
@@ -391,98 +394,101 @@
     <t>Single</t>
   </si>
   <si>
-    <t>24982928 2AP56</t>
+    <t>24982928 2AP70</t>
+  </si>
+  <si>
+    <t>24982928 2AP71</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color indexed="12"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="7"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
       <family val="3"/>
-      <sz val="7"/>
-      <name val="Courier New"/>
     </font>
     <font>
+      <sz val="10"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -505,7 +511,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -522,7 +528,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,24 +548,42 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -956,9 +980,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BZ76"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
     <col min="2" max="2" width="72.6328125" customWidth="1"/>
@@ -1038,7 +1062,7 @@
     <col min="77" max="77" width="22.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.4" customHeight="1" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:77" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1241,212 +1265,208 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="E2" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="F2" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="G2" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="18" t="s">
         <v>69</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>71</v>
       </c>
       <c r="I2" s="19">
         <v>234456532</v>
       </c>
       <c r="J2" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="20">
+        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
+        <v>45786</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="N2" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="O2" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="L2" s="20">
-        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45779</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="N2" s="21" t="s">
+      <c r="P2" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="Q2" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="R2" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="S2" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="Q2" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="R2" s="22" t="s">
+      <c r="T2" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="U2" s="20">
+        <f t="shared" ref="U2:U3" ca="1" si="1">L2</f>
+        <v>45786</v>
+      </c>
+      <c r="V2" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="S2" s="23" t="s">
+      <c r="W2" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="T2" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="U2" s="20">
-        <f t="shared" ref="U2:U3" si="1">L2</f>
-        <v>45779</v>
-      </c>
-      <c r="V2" s="19" t="s">
+      <c r="X2" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="W2" s="24" t="s">
+      <c r="Y2" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="X2" s="22" t="s">
+      <c r="Z2" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="Y2" s="25" t="s">
+      <c r="AA2" s="26" t="s">
         <v>82</v>
-      </c>
-      <c r="Z2" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA2" s="26" t="s">
-        <v>84</v>
       </c>
       <c r="AB2" s="15">
         <v>40</v>
       </c>
       <c r="AC2" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD2" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE2" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="AD2" s="15" t="s">
+      <c r="AF2" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="AE2" s="20" t="s">
+      <c r="AG2" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="AF2" s="19" t="s">
+      <c r="AH2" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="AG2" s="28" t="s">
+      <c r="AI2" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="AH2" s="19" t="s">
+      <c r="AJ2" s="29" t="s">
         <v>90</v>
-      </c>
-      <c r="AI2" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ2" s="29" t="s">
-        <v>92</v>
       </c>
       <c r="AK2" s="19">
         <v>99</v>
       </c>
       <c r="AL2" s="22">
-        <f t="shared" ref="AL2:AL3" si="2">TODAY()+60</f>
-        <v>45870</v>
+        <f t="shared" ref="AL2:AL3" ca="1" si="2">TODAY()+60</f>
+        <v>45877</v>
       </c>
       <c r="AM2" s="22">
-        <f t="shared" ref="AM2:AM3" si="3">U2</f>
-        <v>45779</v>
+        <f t="shared" ref="AM2:AM3" ca="1" si="3">U2</f>
+        <v>45786</v>
       </c>
       <c r="AN2" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO2" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP2" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="AO2" s="21" t="s">
+      <c r="AQ2" s="20" t="str">
+        <f t="shared" ref="AQ2:AQ3" si="4">AE2</f>
+        <v>N/A</v>
+      </c>
+      <c r="AR2" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="AP2" s="22" t="s">
+      <c r="AS2" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="AQ2" s="20">
-        <f t="shared" ref="AQ2:AQ3" si="4">AE2</f>
-        <v>NaN</v>
-      </c>
-      <c r="AR2" s="15" t="s">
+      <c r="AT2" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="AS2" s="15" t="s">
+      <c r="AU2" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AV2" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="AT2" s="15" t="s">
+      <c r="AW2" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="AU2" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV2" s="31" t="s">
+      <c r="AX2" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AY2" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="AW2" s="22" t="s">
+      <c r="AZ2" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="AX2" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="AY2" s="31" t="s">
+      <c r="BB2" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="AZ2" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="BA2" s="32" t="s">
+      <c r="BC2" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD2" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="BE2" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="BB2" s="22" t="s">
+      <c r="BF2" s="34">
+        <v>10000895720</v>
+      </c>
+      <c r="BG2" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH2" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="BC2" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="BD2" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BE2" s="33" t="s">
+      <c r="BI2" s="34">
+        <v>100845911</v>
+      </c>
+      <c r="BJ2" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="BK2" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="BF2" s="34">
-        <v>10000895708</v>
-      </c>
-      <c r="BG2" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH2" s="33" t="s">
+      <c r="BL2" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="BM2" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="BI2" s="34">
-        <v>100845907</v>
-      </c>
-      <c r="BJ2" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BK2" s="35" t="s">
+      <c r="BN2" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="BL2" s="36" t="s">
+      <c r="BO2" s="33" t="s">
         <v>107</v>
-      </c>
-      <c r="BM2" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN2" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="BO2" s="33" t="s">
-        <v>110</v>
       </c>
       <c r="BP2" s="13"/>
       <c r="BQ2" s="13"/>
@@ -1459,212 +1479,208 @@
       <c r="BX2" s="13"/>
       <c r="BY2" s="13"/>
     </row>
-    <row r="3" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="H3" s="18" t="s">
         <v>112</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>116</v>
       </c>
       <c r="I3" s="19">
         <v>234456532</v>
       </c>
       <c r="J3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="L3" s="20">
+        <f t="shared" ca="1" si="0"/>
+        <v>45786</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="N3" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="O3" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="L3" s="20">
-        <f t="shared" si="0"/>
-        <v>45779</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="N3" s="21" t="s">
+      <c r="P3" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="O3" s="18" t="s">
+      <c r="Q3" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="R3" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="P3" s="21" t="s">
+      <c r="S3" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="Q3" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="R3" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="S3" s="23" t="s">
-        <v>78</v>
-      </c>
       <c r="T3" s="19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="U3" s="20">
-        <f t="shared" si="1"/>
-        <v>45779</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45786</v>
       </c>
       <c r="V3" s="19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="W3" s="24" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="X3" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y3" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z3" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="Y3" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z3" s="22" t="s">
-        <v>83</v>
-      </c>
       <c r="AA3" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AB3" s="15">
         <v>40</v>
       </c>
       <c r="AC3" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD3" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE3" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="AD3" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE3" s="20" t="s">
-        <v>87</v>
-      </c>
       <c r="AF3" s="19" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AG3" s="38">
         <v>251</v>
       </c>
       <c r="AH3" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI3" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ3" s="29" t="s">
         <v>90</v>
-      </c>
-      <c r="AI3" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ3" s="29" t="s">
-        <v>92</v>
       </c>
       <c r="AK3" s="19">
         <v>99</v>
       </c>
       <c r="AL3" s="22">
-        <f t="shared" si="2"/>
-        <v>45870</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45877</v>
       </c>
       <c r="AM3" s="22">
-        <f t="shared" si="3"/>
-        <v>45779</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>45786</v>
       </c>
       <c r="AN3" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="AO3" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP3" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="AQ3" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>N/A</v>
+      </c>
+      <c r="AR3" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS3" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT3" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="AU3" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AV3" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="AW3" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="AX3" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AY3" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="AZ3" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA3" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="BB3" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC3" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD3" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="BE3" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="BF3" s="34">
+        <v>10000895721</v>
+      </c>
+      <c r="BG3" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="BH3" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="BI3" s="34">
+        <v>100845912</v>
+      </c>
+      <c r="BJ3" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="BK3" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="BL3" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="AO3" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP3" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="AQ3" s="20">
-        <f t="shared" si="4"/>
-        <v>NaN</v>
-      </c>
-      <c r="AR3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AS3" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT3" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV3" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="AW3" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="AX3" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="AY3" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="AZ3" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="BA3" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="BB3" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="BC3" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="BD3" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BE3" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="BF3" s="34">
-        <v>10000895709</v>
-      </c>
-      <c r="BG3" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH3" s="33" t="s">
+      <c r="BM3" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="BI3" s="34">
-        <v>100845908</v>
-      </c>
-      <c r="BJ3" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BK3" s="35" t="s">
+      <c r="BN3" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="BL3" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="BM3" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN3" s="33" t="s">
-        <v>109</v>
-      </c>
       <c r="BO3" s="33" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="BP3" s="13"/>
       <c r="BQ3" s="13"/>
@@ -1677,7 +1693,7 @@
       <c r="BX3" s="13"/>
       <c r="BY3" s="13"/>
     </row>
-    <row r="4" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1756,7 +1772,7 @@
       <c r="BX4" s="13"/>
       <c r="BY4" s="13"/>
     </row>
-    <row r="5" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -1835,7 +1851,7 @@
       <c r="BX5" s="13"/>
       <c r="BY5" s="13"/>
     </row>
-    <row r="6" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="37"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1913,7 +1929,7 @@
       <c r="BX6" s="13"/>
       <c r="BY6" s="13"/>
     </row>
-    <row r="7" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="37"/>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -1992,7 +2008,7 @@
       <c r="BX7" s="13"/>
       <c r="BY7" s="13"/>
     </row>
-    <row r="8" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37"/>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -2071,7 +2087,7 @@
       <c r="BX8" s="13"/>
       <c r="BY8" s="13"/>
     </row>
-    <row r="9" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="37"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -2150,7 +2166,7 @@
       <c r="BX9" s="13"/>
       <c r="BY9" s="13"/>
     </row>
-    <row r="10" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="37"/>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -2229,7 +2245,7 @@
       <c r="BX10" s="13"/>
       <c r="BY10" s="13"/>
     </row>
-    <row r="11" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="37"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2308,7 +2324,7 @@
       <c r="BX11" s="13"/>
       <c r="BY11" s="13"/>
     </row>
-    <row r="12" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37"/>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -2387,7 +2403,7 @@
       <c r="BX12" s="13"/>
       <c r="BY12" s="13"/>
     </row>
-    <row r="13" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2466,7 +2482,7 @@
       <c r="BX13" s="13"/>
       <c r="BY13" s="13"/>
     </row>
-    <row r="14" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="37"/>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2545,7 +2561,7 @@
       <c r="BX14" s="13"/>
       <c r="BY14" s="13"/>
     </row>
-    <row r="15" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="37"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2624,7 +2640,7 @@
       <c r="BX15" s="13"/>
       <c r="BY15" s="13"/>
     </row>
-    <row r="16" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37"/>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -2703,7 +2719,7 @@
       <c r="BX16" s="13"/>
       <c r="BY16" s="13"/>
     </row>
-    <row r="17" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -2783,7 +2799,7 @@
       <c r="BY17" s="13"/>
       <c r="BZ17" s="13"/>
     </row>
-    <row r="18" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -2863,7 +2879,7 @@
       <c r="BY18" s="13"/>
       <c r="BZ18" s="13"/>
     </row>
-    <row r="19" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="13"/>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -2943,7 +2959,7 @@
       <c r="BY19" s="13"/>
       <c r="BZ19" s="13"/>
     </row>
-    <row r="20" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -3023,7 +3039,7 @@
       <c r="BY20" s="13"/>
       <c r="BZ20" s="13"/>
     </row>
-    <row r="21" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -3103,7 +3119,7 @@
       <c r="BY21" s="13"/>
       <c r="BZ21" s="13"/>
     </row>
-    <row r="22" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
@@ -3183,7 +3199,7 @@
       <c r="BY22" s="13"/>
       <c r="BZ22" s="13"/>
     </row>
-    <row r="23" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3263,7 +3279,7 @@
       <c r="BY23" s="13"/>
       <c r="BZ23" s="13"/>
     </row>
-    <row r="24" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -3343,7 +3359,7 @@
       <c r="BY24" s="13"/>
       <c r="BZ24" s="13"/>
     </row>
-    <row r="25" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -3423,7 +3439,7 @@
       <c r="BY25" s="13"/>
       <c r="BZ25" s="13"/>
     </row>
-    <row r="26" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
@@ -3503,7 +3519,7 @@
       <c r="BY26" s="13"/>
       <c r="BZ26" s="13"/>
     </row>
-    <row r="27" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -3583,7 +3599,7 @@
       <c r="BY27" s="13"/>
       <c r="BZ27" s="13"/>
     </row>
-    <row r="28" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -3663,7 +3679,7 @@
       <c r="BY28" s="13"/>
       <c r="BZ28" s="13"/>
     </row>
-    <row r="29" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -3743,7 +3759,7 @@
       <c r="BY29" s="13"/>
       <c r="BZ29" s="13"/>
     </row>
-    <row r="30" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3823,7 +3839,7 @@
       <c r="BY30" s="13"/>
       <c r="BZ30" s="13"/>
     </row>
-    <row r="31" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -3903,7 +3919,7 @@
       <c r="BY31" s="13"/>
       <c r="BZ31" s="13"/>
     </row>
-    <row r="32" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="13"/>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
@@ -3983,7 +3999,7 @@
       <c r="BY32" s="13"/>
       <c r="BZ32" s="13"/>
     </row>
-    <row r="33" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="13"/>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -4063,7 +4079,7 @@
       <c r="BY33" s="13"/>
       <c r="BZ33" s="13"/>
     </row>
-    <row r="34" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="13"/>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -4143,7 +4159,7 @@
       <c r="BY34" s="13"/>
       <c r="BZ34" s="13"/>
     </row>
-    <row r="35" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="13"/>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -4223,7 +4239,7 @@
       <c r="BY35" s="13"/>
       <c r="BZ35" s="13"/>
     </row>
-    <row r="36" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="13"/>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
@@ -4303,7 +4319,7 @@
       <c r="BY36" s="13"/>
       <c r="BZ36" s="13"/>
     </row>
-    <row r="37" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="13"/>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
@@ -4383,7 +4399,7 @@
       <c r="BY37" s="13"/>
       <c r="BZ37" s="13"/>
     </row>
-    <row r="38" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="13"/>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -4463,7 +4479,7 @@
       <c r="BY38" s="13"/>
       <c r="BZ38" s="13"/>
     </row>
-    <row r="39" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="13"/>
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
@@ -4543,7 +4559,7 @@
       <c r="BY39" s="13"/>
       <c r="BZ39" s="13"/>
     </row>
-    <row r="40" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="13"/>
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
@@ -4623,7 +4639,7 @@
       <c r="BY40" s="13"/>
       <c r="BZ40" s="13"/>
     </row>
-    <row r="41" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="13"/>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -4703,7 +4719,7 @@
       <c r="BY41" s="13"/>
       <c r="BZ41" s="13"/>
     </row>
-    <row r="42" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="13"/>
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
@@ -4783,7 +4799,7 @@
       <c r="BY42" s="13"/>
       <c r="BZ42" s="13"/>
     </row>
-    <row r="43" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="13"/>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4863,7 +4879,7 @@
       <c r="BY43" s="13"/>
       <c r="BZ43" s="13"/>
     </row>
-    <row r="44" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
@@ -4943,7 +4959,7 @@
       <c r="BY44" s="13"/>
       <c r="BZ44" s="13"/>
     </row>
-    <row r="45" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="13"/>
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
@@ -5023,7 +5039,7 @@
       <c r="BY45" s="13"/>
       <c r="BZ45" s="13"/>
     </row>
-    <row r="46" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="13"/>
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
@@ -5103,7 +5119,7 @@
       <c r="BY46" s="13"/>
       <c r="BZ46" s="13"/>
     </row>
-    <row r="47" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="13"/>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
@@ -5183,7 +5199,7 @@
       <c r="BY47" s="13"/>
       <c r="BZ47" s="13"/>
     </row>
-    <row r="48" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="13"/>
       <c r="B48" s="13"/>
       <c r="C48" s="13"/>
@@ -5263,7 +5279,7 @@
       <c r="BY48" s="13"/>
       <c r="BZ48" s="13"/>
     </row>
-    <row r="49" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="13"/>
       <c r="B49" s="13"/>
       <c r="C49" s="13"/>
@@ -5343,7 +5359,7 @@
       <c r="BY49" s="13"/>
       <c r="BZ49" s="13"/>
     </row>
-    <row r="50" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="13"/>
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
@@ -5423,7 +5439,7 @@
       <c r="BY50" s="13"/>
       <c r="BZ50" s="13"/>
     </row>
-    <row r="51" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="13"/>
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
@@ -5503,7 +5519,7 @@
       <c r="BY51" s="13"/>
       <c r="BZ51" s="13"/>
     </row>
-    <row r="52" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="13"/>
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
@@ -5583,7 +5599,7 @@
       <c r="BY52" s="13"/>
       <c r="BZ52" s="13"/>
     </row>
-    <row r="53" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="13"/>
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
@@ -5663,7 +5679,7 @@
       <c r="BY53" s="13"/>
       <c r="BZ53" s="13"/>
     </row>
-    <row r="54" ht="14.5" customHeight="1" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:78" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="13"/>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
@@ -5743,78 +5759,78 @@
       <c r="BY54" s="13"/>
       <c r="BZ54" s="13"/>
     </row>
-    <row r="55" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F55" s="13"/>
     </row>
-    <row r="56" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F56" s="13"/>
     </row>
-    <row r="57" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F57" s="13"/>
     </row>
-    <row r="58" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F58" s="13"/>
     </row>
-    <row r="59" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F59" s="13"/>
     </row>
-    <row r="60" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F60" s="13"/>
     </row>
-    <row r="61" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F61" s="13"/>
     </row>
-    <row r="62" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F62" s="13"/>
     </row>
-    <row r="63" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F63" s="13"/>
     </row>
-    <row r="64" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F64" s="13"/>
     </row>
-    <row r="65" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F65" s="13"/>
     </row>
-    <row r="66" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F66" s="13"/>
     </row>
-    <row r="67" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F67" s="13"/>
     </row>
-    <row r="68" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F68" s="13"/>
     </row>
-    <row r="69" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F69" s="13"/>
     </row>
-    <row r="70" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F70" s="13"/>
     </row>
-    <row r="71" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F71" s="13"/>
     </row>
-    <row r="72" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F72" s="13"/>
     </row>
-    <row r="73" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F73" s="13"/>
     </row>
-    <row r="74" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F74" s="13"/>
     </row>
-    <row r="75" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F75" s="13"/>
     </row>
-    <row r="76" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F76" s="13"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1"/>
-    <hyperlink ref="S3" r:id="rId2"/>
+    <hyperlink ref="S2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/27/Workday_NewHire_Portugal_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_Portugal_Regression_PK17.xlsx
@@ -1,38 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{1C6E3993-62BE-490C-B14A-B5F32166C46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BY$53</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="125">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -229,16 +214,22 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t>10699792</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>420 Recruitment (Gozyb Sosobo (10034456))</t>
   </si>
   <si>
     <t>Portugal</t>
   </si>
   <si>
-    <t>Evelyn</t>
-  </si>
-  <si>
-    <t>Grimes</t>
+    <t>Kennith</t>
+  </si>
+  <si>
+    <t>Howe</t>
   </si>
   <si>
     <t>Sr.</t>
@@ -349,6 +340,9 @@
     <t>ID Number (Numero de</t>
   </si>
   <si>
+    <t>24982928 2AP80</t>
+  </si>
+  <si>
     <t>BBVAESMM128</t>
   </si>
   <si>
@@ -361,13 +355,16 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t>10699794</t>
+  </si>
+  <si>
     <t>420 Store Management (Rilyv Zisozy (4206015))</t>
   </si>
   <si>
-    <t>Nathanael</t>
-  </si>
-  <si>
-    <t>Waters-Mann</t>
+    <t>Cassie</t>
+  </si>
+  <si>
+    <t>Christiansen</t>
   </si>
   <si>
     <t>Sra.</t>
@@ -376,7 +373,7 @@
     <t>New</t>
   </si>
   <si>
-    <t>Auto 79934795</t>
+    <t>Auto 96123479</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -394,101 +391,98 @@
     <t>Single</t>
   </si>
   <si>
-    <t>24982928 2AP70</t>
-  </si>
-  <si>
-    <t>24982928 2AP71</t>
+    <t>24982928 2AP81</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color indexed="8"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
+      <color indexed="12"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color indexed="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1F1F1F"/>
+      <family val="3"/>
       <sz val="7"/>
-      <color rgb="FF1F1F1F"/>
       <name val="Courier New"/>
-      <family val="3"/>
     </font>
     <font>
-      <sz val="10"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -511,7 +505,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -528,7 +522,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,42 +542,24 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -980,9 +956,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BZ76"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
     <col min="2" max="2" width="72.6328125" customWidth="1"/>
@@ -1062,7 +1038,7 @@
     <col min="77" max="77" width="22.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="17.4" customHeight="1" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1265,208 +1241,212 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="13"/>
+      <c r="B2" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>66</v>
+      </c>
       <c r="D2" s="14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I2" s="19">
         <v>234456532</v>
       </c>
       <c r="J2" s="19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K2" s="19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L2" s="20">
-        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45786</v>
+        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
+        <v>45796</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O2" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="P2" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="P2" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q2" s="19" t="s">
-        <v>71</v>
-      </c>
       <c r="R2" s="22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="S2" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T2" s="19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="U2" s="20">
-        <f t="shared" ref="U2:U3" ca="1" si="1">L2</f>
-        <v>45786</v>
+        <f t="shared" ref="U2:U3" si="1">L2</f>
+        <v>45796</v>
       </c>
       <c r="V2" s="19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W2" s="24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="X2" s="22" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Y2" s="25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Z2" s="22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AA2" s="26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AB2" s="15">
         <v>40</v>
       </c>
       <c r="AC2" s="27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AD2" s="15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AE2" s="20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AF2" s="19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AG2" s="28" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AH2" s="19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI2" s="29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ2" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK2" s="19">
         <v>99</v>
       </c>
       <c r="AL2" s="22">
-        <f t="shared" ref="AL2:AL3" ca="1" si="2">TODAY()+60</f>
-        <v>45877</v>
+        <f t="shared" ref="AL2:AL3" si="2">TODAY()+60</f>
+        <v>45887</v>
       </c>
       <c r="AM2" s="22">
-        <f t="shared" ref="AM2:AM3" ca="1" si="3">U2</f>
-        <v>45786</v>
+        <f t="shared" ref="AM2:AM3" si="3">U2</f>
+        <v>45796</v>
       </c>
       <c r="AN2" s="30" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO2" s="21" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AP2" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="AQ2" s="20" t="str">
+        <v>95</v>
+      </c>
+      <c r="AQ2" s="20">
         <f t="shared" ref="AQ2:AQ3" si="4">AE2</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AR2" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS2" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AT2" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="AU2" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="AU2" s="15" t="s">
-        <v>94</v>
-      </c>
       <c r="AV2" s="31" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AW2" s="22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AX2" s="31" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AY2" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AZ2" s="31" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="BA2" s="32" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BB2" s="22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BC2" s="32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BD2" s="33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BE2" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BF2" s="34">
-        <v>10000895720</v>
+        <v>10000895750</v>
       </c>
       <c r="BG2" s="33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BH2" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BI2" s="34">
-        <v>100845911</v>
+        <v>100845920</v>
       </c>
       <c r="BJ2" s="33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BK2" s="35" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BL2" s="36" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="BM2" s="33" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BN2" s="33" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="BO2" s="33" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="BP2" s="13"/>
       <c r="BQ2" s="13"/>
@@ -1479,208 +1459,212 @@
       <c r="BX2" s="13"/>
       <c r="BY2" s="13"/>
     </row>
-    <row r="3" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
+        <v>111</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>66</v>
+      </c>
       <c r="D3" s="14" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I3" s="19">
         <v>234456532</v>
       </c>
       <c r="J3" s="19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K3" s="19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L3" s="20">
-        <f t="shared" ca="1" si="0"/>
-        <v>45786</v>
+        <f t="shared" si="0"/>
+        <v>45796</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O3" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q3" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="P3" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q3" s="19" t="s">
-        <v>71</v>
-      </c>
       <c r="R3" s="22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="S3" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T3" s="19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="U3" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>45786</v>
+        <f t="shared" si="1"/>
+        <v>45796</v>
       </c>
       <c r="V3" s="19" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="W3" s="24" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="X3" s="22" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Y3" s="25" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="Z3" s="22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AA3" s="26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AB3" s="15">
         <v>40</v>
       </c>
       <c r="AC3" s="27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AD3" s="15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AE3" s="20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AF3" s="19" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG3" s="38">
         <v>251</v>
       </c>
       <c r="AH3" s="19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI3" s="29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ3" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK3" s="19">
         <v>99</v>
       </c>
       <c r="AL3" s="22">
-        <f t="shared" ca="1" si="2"/>
-        <v>45877</v>
+        <f t="shared" si="2"/>
+        <v>45887</v>
       </c>
       <c r="AM3" s="22">
-        <f t="shared" ca="1" si="3"/>
-        <v>45786</v>
+        <f t="shared" si="3"/>
+        <v>45796</v>
       </c>
       <c r="AN3" s="30" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AO3" s="21" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AP3" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="AQ3" s="20" t="str">
+        <v>95</v>
+      </c>
+      <c r="AQ3" s="20">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AR3" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS3" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AT3" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AU3" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AV3" s="31" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="AW3" s="22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AX3" s="31" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AY3" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AZ3" s="31" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="BA3" s="32" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="BB3" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="BC3" s="32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BD3" s="33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BE3" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BF3" s="34">
-        <v>10000895721</v>
+        <v>10000895751</v>
       </c>
       <c r="BG3" s="33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BH3" s="33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BI3" s="34">
-        <v>100845912</v>
+        <v>100845921</v>
       </c>
       <c r="BJ3" s="33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BK3" s="35" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BL3" s="36" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="BM3" s="33" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BN3" s="33" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="BO3" s="33" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="BP3" s="13"/>
       <c r="BQ3" s="13"/>
@@ -1693,7 +1677,7 @@
       <c r="BX3" s="13"/>
       <c r="BY3" s="13"/>
     </row>
-    <row r="4" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1772,7 +1756,7 @@
       <c r="BX4" s="13"/>
       <c r="BY4" s="13"/>
     </row>
-    <row r="5" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -1851,7 +1835,7 @@
       <c r="BX5" s="13"/>
       <c r="BY5" s="13"/>
     </row>
-    <row r="6" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="37"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1929,7 +1913,7 @@
       <c r="BX6" s="13"/>
       <c r="BY6" s="13"/>
     </row>
-    <row r="7" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="37"/>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -2008,7 +1992,7 @@
       <c r="BX7" s="13"/>
       <c r="BY7" s="13"/>
     </row>
-    <row r="8" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37"/>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -2087,7 +2071,7 @@
       <c r="BX8" s="13"/>
       <c r="BY8" s="13"/>
     </row>
-    <row r="9" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="37"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -2166,7 +2150,7 @@
       <c r="BX9" s="13"/>
       <c r="BY9" s="13"/>
     </row>
-    <row r="10" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="37"/>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -2245,7 +2229,7 @@
       <c r="BX10" s="13"/>
       <c r="BY10" s="13"/>
     </row>
-    <row r="11" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="37"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2324,7 +2308,7 @@
       <c r="BX11" s="13"/>
       <c r="BY11" s="13"/>
     </row>
-    <row r="12" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37"/>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -2403,7 +2387,7 @@
       <c r="BX12" s="13"/>
       <c r="BY12" s="13"/>
     </row>
-    <row r="13" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2482,7 +2466,7 @@
       <c r="BX13" s="13"/>
       <c r="BY13" s="13"/>
     </row>
-    <row r="14" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="37"/>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2561,7 +2545,7 @@
       <c r="BX14" s="13"/>
       <c r="BY14" s="13"/>
     </row>
-    <row r="15" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="37"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2640,7 +2624,7 @@
       <c r="BX15" s="13"/>
       <c r="BY15" s="13"/>
     </row>
-    <row r="16" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37"/>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -2719,7 +2703,7 @@
       <c r="BX16" s="13"/>
       <c r="BY16" s="13"/>
     </row>
-    <row r="17" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -2799,7 +2783,7 @@
       <c r="BY17" s="13"/>
       <c r="BZ17" s="13"/>
     </row>
-    <row r="18" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -2879,7 +2863,7 @@
       <c r="BY18" s="13"/>
       <c r="BZ18" s="13"/>
     </row>
-    <row r="19" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -2959,7 +2943,7 @@
       <c r="BY19" s="13"/>
       <c r="BZ19" s="13"/>
     </row>
-    <row r="20" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -3039,7 +3023,7 @@
       <c r="BY20" s="13"/>
       <c r="BZ20" s="13"/>
     </row>
-    <row r="21" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -3119,7 +3103,7 @@
       <c r="BY21" s="13"/>
       <c r="BZ21" s="13"/>
     </row>
-    <row r="22" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
@@ -3199,7 +3183,7 @@
       <c r="BY22" s="13"/>
       <c r="BZ22" s="13"/>
     </row>
-    <row r="23" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3279,7 +3263,7 @@
       <c r="BY23" s="13"/>
       <c r="BZ23" s="13"/>
     </row>
-    <row r="24" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -3359,7 +3343,7 @@
       <c r="BY24" s="13"/>
       <c r="BZ24" s="13"/>
     </row>
-    <row r="25" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -3439,7 +3423,7 @@
       <c r="BY25" s="13"/>
       <c r="BZ25" s="13"/>
     </row>
-    <row r="26" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
@@ -3519,7 +3503,7 @@
       <c r="BY26" s="13"/>
       <c r="BZ26" s="13"/>
     </row>
-    <row r="27" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -3599,7 +3583,7 @@
       <c r="BY27" s="13"/>
       <c r="BZ27" s="13"/>
     </row>
-    <row r="28" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -3679,7 +3663,7 @@
       <c r="BY28" s="13"/>
       <c r="BZ28" s="13"/>
     </row>
-    <row r="29" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -3759,7 +3743,7 @@
       <c r="BY29" s="13"/>
       <c r="BZ29" s="13"/>
     </row>
-    <row r="30" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3839,7 +3823,7 @@
       <c r="BY30" s="13"/>
       <c r="BZ30" s="13"/>
     </row>
-    <row r="31" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -3919,7 +3903,7 @@
       <c r="BY31" s="13"/>
       <c r="BZ31" s="13"/>
     </row>
-    <row r="32" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13"/>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
@@ -3999,7 +3983,7 @@
       <c r="BY32" s="13"/>
       <c r="BZ32" s="13"/>
     </row>
-    <row r="33" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13"/>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -4079,7 +4063,7 @@
       <c r="BY33" s="13"/>
       <c r="BZ33" s="13"/>
     </row>
-    <row r="34" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13"/>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -4159,7 +4143,7 @@
       <c r="BY34" s="13"/>
       <c r="BZ34" s="13"/>
     </row>
-    <row r="35" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -4239,7 +4223,7 @@
       <c r="BY35" s="13"/>
       <c r="BZ35" s="13"/>
     </row>
-    <row r="36" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13"/>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
@@ -4319,7 +4303,7 @@
       <c r="BY36" s="13"/>
       <c r="BZ36" s="13"/>
     </row>
-    <row r="37" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
@@ -4399,7 +4383,7 @@
       <c r="BY37" s="13"/>
       <c r="BZ37" s="13"/>
     </row>
-    <row r="38" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -4479,7 +4463,7 @@
       <c r="BY38" s="13"/>
       <c r="BZ38" s="13"/>
     </row>
-    <row r="39" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
@@ -4559,7 +4543,7 @@
       <c r="BY39" s="13"/>
       <c r="BZ39" s="13"/>
     </row>
-    <row r="40" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
@@ -4639,7 +4623,7 @@
       <c r="BY40" s="13"/>
       <c r="BZ40" s="13"/>
     </row>
-    <row r="41" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -4719,7 +4703,7 @@
       <c r="BY41" s="13"/>
       <c r="BZ41" s="13"/>
     </row>
-    <row r="42" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
@@ -4799,7 +4783,7 @@
       <c r="BY42" s="13"/>
       <c r="BZ42" s="13"/>
     </row>
-    <row r="43" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4879,7 +4863,7 @@
       <c r="BY43" s="13"/>
       <c r="BZ43" s="13"/>
     </row>
-    <row r="44" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
@@ -4959,7 +4943,7 @@
       <c r="BY44" s="13"/>
       <c r="BZ44" s="13"/>
     </row>
-    <row r="45" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="13"/>
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
@@ -5039,7 +5023,7 @@
       <c r="BY45" s="13"/>
       <c r="BZ45" s="13"/>
     </row>
-    <row r="46" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13"/>
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
@@ -5119,7 +5103,7 @@
       <c r="BY46" s="13"/>
       <c r="BZ46" s="13"/>
     </row>
-    <row r="47" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="13"/>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
@@ -5199,7 +5183,7 @@
       <c r="BY47" s="13"/>
       <c r="BZ47" s="13"/>
     </row>
-    <row r="48" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13"/>
       <c r="B48" s="13"/>
       <c r="C48" s="13"/>
@@ -5279,7 +5263,7 @@
       <c r="BY48" s="13"/>
       <c r="BZ48" s="13"/>
     </row>
-    <row r="49" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13"/>
       <c r="B49" s="13"/>
       <c r="C49" s="13"/>
@@ -5359,7 +5343,7 @@
       <c r="BY49" s="13"/>
       <c r="BZ49" s="13"/>
     </row>
-    <row r="50" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13"/>
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
@@ -5439,7 +5423,7 @@
       <c r="BY50" s="13"/>
       <c r="BZ50" s="13"/>
     </row>
-    <row r="51" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13"/>
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
@@ -5519,7 +5503,7 @@
       <c r="BY51" s="13"/>
       <c r="BZ51" s="13"/>
     </row>
-    <row r="52" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="13"/>
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
@@ -5599,7 +5583,7 @@
       <c r="BY52" s="13"/>
       <c r="BZ52" s="13"/>
     </row>
-    <row r="53" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="13"/>
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
@@ -5679,7 +5663,7 @@
       <c r="BY53" s="13"/>
       <c r="BZ53" s="13"/>
     </row>
-    <row r="54" spans="1:78" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" ht="14.5" customHeight="1" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A54" s="13"/>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
@@ -5759,78 +5743,78 @@
       <c r="BY54" s="13"/>
       <c r="BZ54" s="13"/>
     </row>
-    <row r="55" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F55" s="13"/>
     </row>
-    <row r="56" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F56" s="13"/>
     </row>
-    <row r="57" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F57" s="13"/>
     </row>
-    <row r="58" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F58" s="13"/>
     </row>
-    <row r="59" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F59" s="13"/>
     </row>
-    <row r="60" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F60" s="13"/>
     </row>
-    <row r="61" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F61" s="13"/>
     </row>
-    <row r="62" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F62" s="13"/>
     </row>
-    <row r="63" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F63" s="13"/>
     </row>
-    <row r="64" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F64" s="13"/>
     </row>
-    <row r="65" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F65" s="13"/>
     </row>
-    <row r="66" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F66" s="13"/>
     </row>
-    <row r="67" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F67" s="13"/>
     </row>
-    <row r="68" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F68" s="13"/>
     </row>
-    <row r="69" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F69" s="13"/>
     </row>
-    <row r="70" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F70" s="13"/>
     </row>
-    <row r="71" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F71" s="13"/>
     </row>
-    <row r="72" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F72" s="13"/>
     </row>
-    <row r="73" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F73" s="13"/>
     </row>
-    <row r="74" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F74" s="13"/>
     </row>
-    <row r="75" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F75" s="13"/>
     </row>
-    <row r="76" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F76" s="13"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="S3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="S2" r:id="rId1"/>
+    <hyperlink ref="S3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>